--- a/medford_lor_kresla.xlsx
+++ b/medford_lor_kresla.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Какие хорошие бренды кресел?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>lor_kresla</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Как называется кресло гинеколога?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>lor_kresla</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>

--- a/medford_lor_kresla.xlsx
+++ b/medford_lor_kresla.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-кресла для оснащения клиник и медицинских учреждений. В каталоге представлено 20 позиций.</t>
+          <t>ЛОР-кресла для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lor_kresla.xlsx
+++ b/medford_lor_kresla.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать лОР-кресла для клиники?</t>
+          <t>Чем ЛОР-кресло отличается от стула врача?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Угол поворота кресла, °, Базовая длина, мм, Страна производства, Производитель). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Кресло пациента предназначено для размещения пациента при осмотре и процедурах, оснащается регулировкой высоты, наклона спинки, подголовника и поворотом вокруг оси. Стул врача — рабочее место оториноларинголога с регулировкой по высоте. Это разные изделия, и в каталоге они представлены отдельными группами; выбирают их под соответствующую задачу.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Сколько моторов должно быть у кресла пациента?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Число моторов определяет, сколько положений регулируется электроприводом. Двухмоторные модели (Otopex Euroclinic) настраивают базовые параметры, четырёхмоторные (Euroclinic Lynea EVO) дают более тонкую и независимую регулировку высоты, спинки и подголовника. Нужное число моторов подбирают под характер и частоту процедур в кабинете.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>На какой угол поворачивается ЛОР-кресло?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Угол поворота вокруг оси у моделей каталога — от 90° до 360°. Например, Otopex поворачивается на 90°, Euroclinic Lynea EVO на 175°, Xenon EVO и Oto P/V на 360°, Clear КЛЭМ на 240° или 300° в зависимости от положения спинки. Больший угол упрощает доступ врача к пациенту с разных сторон.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Можно ли управлять креслом с ЛОР-комбайна?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Многие кресла пациента управляются с панели ЛОР-установки, что синхронизирует их с рабочим местом врача. Если кресло приобретают к имеющемуся комбайну, совместимость управления и креплений уточняют заранее по документации обоих изделий. При автономном использовании кресло работает от собственной панели управления.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Из чего делают обивку ЛОР-кресел?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Обивку выполняют из гипоаллергенных материалов, устойчивых к регулярной обработке дезинфицирующими растворами, а конструкцию рассчитывают на ежедневную интенсивную эксплуатацию. Конкретный материал и перечень допустимых средств обработки указывает производитель в спецификации модели. Устойчивость к дезинфекции влияет на срок службы кресла и санитарную безопасность кабинета.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Какие хорошие бренды кресел?</t>
+          <t>Как подобрать кресло по размеру кабинета?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Учитывают базовую длину и габариты кресла: у части моделей Euroclinic базовая длина составляет 740–800 мм. Кресло должно оставлять врачу место для доступа с нужных сторон и для работы с ЛОР-комбайном или инструментами. Точные габариты и радиус поворота сверяют с планировкой кабинета до приобретения.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Как называется кресло гинеколога?</t>
+          <t>Нужно ли регистрационное удостоверение?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да. ЛОР-кресло — медицинское изделие, которое вводят в оборот при действующем регистрационном удостоверении Росздравнадзора на модель. Перед приобретением сверяют статус РУ, для электрических кресел — параметры электропитания, а также условия сервисного обслуживания и доступность запчастей у поставщика.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-кресла для оснащения клиник и медицинских учреждений.</t>
+          <t>ЛОР-кресла обеспечивают удобное и стабильное положение пациента при осмотре уха, горла и носа, диагностике и амбулаторных процедурах в отоларингологии. В каталоге собраны кресла пациента Euroclinic, MEGA MEDICAL, Medstar, Clear, Zerts, Otopront и Otopex, а также стулья ЛОР-врача Mega Medical и Euroclinic. Кресла пациента различаются углом поворота вокруг оси — от 90° до 360° — и числом моторов регулировки: например, Euroclinic Lynea EVO четырёхмоторное с поворотом 175°, а Xenon EVO поворачивается на 360°. Регулировка по высоте у моделей MEGA MEDICAL составляет 500–800 мм.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>ЛОР-кресло пациента и стул врача</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР-кресла</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4394,227 +4394,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — ЛОР-кресло пациента и стул врача</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Кресло пациента</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Угол поворота кресла, °</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Базовая длина, мм</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
+          <t>Стул врача</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mega Medical стул ЛОР врача со спинкой</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Назначение</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>размещение пациента при осмотре и процедурах</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>рабочее место оториноларинголога</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Otopex Euroclinic кресло отоларингологическое, двухмоторное</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Привод</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>часто электрический, 2–4 мотора</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>механический</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MEGA MEDICAL NET-1500A ЛОР-кресло пациента</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>Регулировки</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>высота, спинка, подголовник, поворот до 360°</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>регулировка по высоте (например, 450–560 мм)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Euroclinic SPD/A стул врача ЛОРа</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>Примеры</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Euroclinic Lynea EVO, MEGA MEDICAL NET-1500, Clear КЛЭМ</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Италия</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>67362</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Otopront SIT 4 кресло отоларингологическое</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>360° с механизмом фиксации на 90°</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Euroclinic Lynea EVO ЛОР-кресло пациента, четырехмоторное</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mega Medical, Euroclinic SPD, Medstar</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4626,7 +4508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4952,12 +4834,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Разделите кресло пациента и стул врача</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается лОР-кресла: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала определяют, что именно нужно: кресло пациента для размещения при осмотре и процедурах или стул врача как рабочее место оториноларинголога. В каталоге есть обе группы — кресла Euroclinic, MEGA MEDICAL, Medstar, Clear и стулья Mega Medical, Euroclinic SPD. Это разные изделия, и характеристики у них не сопоставляются напрямую.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4997,12 +4879,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите тип привода</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Кресла пациента бывают с электроприводом на два-четыре мотора: двухмоторное Otopex Euroclinic, четырёхмоторное Euroclinic Lynea EVO. Больше моторов — больше независимых регулировок высоты, спинки и подголовника. Стулья врача обычно с механической регулировкой по высоте (например, Mega Medical 450–560 мм). Тип привода подбирают под характер и частоту процедур.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5042,12 +4924,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените угол поворота и регулировки</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Угол поворота кресла, °, Базовая длина, мм, Страна производства, Производитель. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Угол поворота кресла вокруг оси в каталоге — от 90° до 360°: Otopex 90°, Lynea EVO 175°, Xenon EVO и Oto P/V 360°, Clear КЛЭМ 240°/300° в зависимости от положения спинки. Поворот и регулировка высоты (у MEGA MEDICAL 500–800 мм) обеспечивают удобный доступ врача. Нужный диапазон определяют по планируемым манипуляциям.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5087,12 +4969,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте совместимость с ЛОР-комбайном</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Многие кресла пациента управляются с панели ЛОР-установки, что синхронизирует их с рабочим местом врача. Если кресло приобретают к имеющемуся комбайну, совместимость управления и креплений уточняют заранее. При автономном использовании этот пункт не критичен. Требования к интеграции сверяют по документации производителей обоих изделий.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5132,12 +5014,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите материалы и гигиену</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Обивка ЛОР-кресел выполняется из гипоаллергенных материалов, устойчивых к регулярной обработке дезинфицирующими растворами, а конструкция рассчитана на ежедневную интенсивную эксплуатацию. Конкретный материал и допустимые средства обработки уточняют по спецификации модели. Устойчивость к дезинфекции напрямую влияет на срок службы и соблюдение санитарных требований кабинета.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5177,12 +5059,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните габариты, питание и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Проверяют базовую длину и габариты кресла под площадь кабинета (у части моделей Euroclinic базовая длина 740–800 мм), а для электрических кресел — параметры электропитания. Перед вводом в оборот сверяют регистрационное удостоверение Росздравнадзора на модель и условия сервисного обслуживания у поставщика.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5232,7 +5114,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-кресла подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на угол поворота кресла, базовая длина, страна производства, производитель, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Первое, что нужно разделять, — кресло пациента и стул врача: это разные изделия под разные задачи. У кресла пациента я смотрю на число моторов и объём регулировок: четырёхмоторные модели вроде Euroclinic Lynea EVO дают тонкую настройку положения, что важно при процедурах. Угол поворота вокруг оси в каталоге доходит до 360°. Если кресло будет работать в связке с ЛОР-комбайном, совместимость управления проверяю заранее.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5516,13 +5398,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР-кресла</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ЛОР-кресла — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>ЛОР-кресло — специализированное кресло для размещения пациента при отоларингологическом осмотре, диагностике и малых амбулаторных процедурах. В каталоге две группы: кресла пациента (Euroclinic, MEGA MEDICAL, Medstar, Clear, Zerts) с электроприводом, регулировкой высоты, наклона спинки и поворотом вокруг оси до 360°, и стулья ЛОР-врача с механической регулировкой по высоте. Кресла пациента часто управляются с панели ЛОР-комбайна. При выборе оценивают тип изделия (кресло пациента или стул врача), число моторов привода, угол поворота, габариты и совместимость с установкой кабинета.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5559,13 +5441,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое ЛОР-кресло</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Угол поворота кресла, °, Базовая длина, мм, Страна производства, Производитель), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>ЛОР-кресло — специализированное медицинское кресло для размещения пациента при осмотре, диагностике и амбулаторных процедурах в отоларингологии. Оно обеспечивает удобное и стабильное положение при исследовании уха, горла и носа. Современные модели оснащают электроприводом для регулировки высоты, наклона спинки, подголовника и поворота вокруг оси.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5602,13 +5484,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Кресло пациента и стул врача</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>В каталоге две группы изделий. Кресла пациента (Euroclinic, MEGA MEDICAL, Medstar, Clear, Zerts, Otopront) размещают пациента и имеют электропривод и поворот до 360°. Стулья ЛОР-врача (Mega Medical, Euroclinic SPD) — рабочее место специалиста с регулировкой по высоте. Это разные изделия под разные задачи оснащения кабинета.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5645,13 +5527,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Как выбрать ЛОР-кресло</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Сначала определяют тип — кресло пациента или стул врача. Для кресла пациента оценивают число моторов привода (2–4), угол поворота (90–360°), диапазон регулировки высоты и базовые габариты под кабинет. Проверяют совместимость с ЛОР-комбайном, если кресло приобретают к установке, а также устойчивость обивки к дезинфекции.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5668,6 +5550,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Материалы и эксплуатация</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Обивку ЛОР-кресел делают из гипоаллергенных материалов, устойчивых к дезинфицирующим растворам, а конструкцию рассчитывают на ежедневную интенсивную работу. Перед вводом в оборот проверяют регистрационное удостоверение Росздравнадзора, параметры электропитания для моторных моделей и условия сервиса. Правильная обработка обивки продлевает срок службы и поддерживает санитарные требования.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lor_kresla</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
